--- a/simulations/correction_peat_market/impact_brut_2 - Copie.xlsx
+++ b/simulations/correction_peat_market/impact_brut_2 - Copie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37324BFE-2F0E-4A09-B9C0-3E9F142FA086}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DD53F8-5FB7-46F4-A87E-95506238E84F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
   <si>
     <t>Process</t>
   </si>
@@ -397,7 +397,7 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="28">
           <cell r="C28">
@@ -435,19 +435,19 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
       <sheetData sheetId="15">
         <row r="75">
           <cell r="C75">
@@ -455,10 +455,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
       <sheetData sheetId="20">
         <row r="43">
           <cell r="C43">
@@ -466,13 +466,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -513,7 +513,7 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="AC4">
@@ -540,33 +540,33 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -583,8 +583,8 @@
       <sheetName val="Direct impact contributions"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="33">
           <cell r="F33">
@@ -597,8 +597,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -724,7 +724,13 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="102">
+          <cell r="AG102">
+            <v>-69.344039327523348</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
@@ -747,14 +753,50 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
+      <sheetData sheetId="14">
+        <row r="99">
+          <cell r="AG99">
+            <v>-79.632739323069075</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="15">
+        <row r="80">
+          <cell r="AG80">
+            <v>51.618888337340763</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16">
+        <row r="98">
+          <cell r="AG98">
+            <v>-28.322830408818469</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17">
+        <row r="83">
+          <cell r="AG83">
+            <v>10.59767941863592</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
+      <sheetData sheetId="20">
+        <row r="81">
+          <cell r="AG81">
+            <v>0.30897942309017878</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="21">
+        <row r="84">
+          <cell r="AG84">
+            <v>56.408704609001795</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
@@ -768,6 +810,199 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="IW+_end"/>
+      <sheetName val="LCI_AD-f"/>
+      <sheetName val="LCIA_AD-f"/>
+      <sheetName val="LCIA_AD-d"/>
+      <sheetName val="LCIA_AD-c"/>
+      <sheetName val="LCI_AD-e"/>
+      <sheetName val="Waste_characteristics"/>
+      <sheetName val="Parameters"/>
+      <sheetName val="LCI"/>
+      <sheetName val="LCI_AD-d"/>
+      <sheetName val="params_HC"/>
+      <sheetName val="LCI_AD-a"/>
+      <sheetName val="LCI_AD-c"/>
+      <sheetName val="LCI_HC"/>
+      <sheetName val="LCI_AD-b"/>
+      <sheetName val="LCIA_AD-b"/>
+      <sheetName val="LCIA_HC"/>
+      <sheetName val="LCIA_AD-e"/>
+      <sheetName val="Figures"/>
+      <sheetName val="Figures_transport"/>
+      <sheetName val="IW+f"/>
+      <sheetName val="LCIA_AD-a"/>
+      <sheetName val="LCIA_IC"/>
+      <sheetName val="LCI_IC"/>
+      <sheetName val="AD_a_end"/>
+      <sheetName val="impact_process_end"/>
+      <sheetName val="impact_process_mid"/>
+      <sheetName val="IW+_mid"/>
+      <sheetName val="IC_end"/>
+      <sheetName val="AD_a_mid"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="5">
+          <cell r="C5">
+            <v>84.546284038232599</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="C51">
+            <v>-215.85245782181113</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="AG56">
+            <v>46.038360226339158</v>
+          </cell>
+          <cell r="AH56">
+            <v>4.8370041166785849E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="5">
+          <cell r="C5">
+            <v>150.20130726777239</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="AG54">
+            <v>86.06842941813477</v>
+          </cell>
+          <cell r="AH54">
+            <v>6.9920169042280941E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="5">
+          <cell r="C5">
+            <v>166.06528020235362</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AG45">
+            <v>76.859354005042192</v>
+          </cell>
+          <cell r="AH45">
+            <v>6.3197861038764738E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15">
+        <row r="5">
+          <cell r="C5">
+            <v>115.03586225244955</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="AG55">
+            <v>44.143274255280637</v>
+          </cell>
+          <cell r="AH55">
+            <v>5.0297485870563373E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16">
+        <row r="30">
+          <cell r="AG30">
+            <v>45.531422488575686</v>
+          </cell>
+          <cell r="AH30">
+            <v>1.5340506341983027E-4</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="C70">
+            <v>34.264521044421535</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17">
+        <row r="5">
+          <cell r="C5">
+            <v>100.41025697281384</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>-215.01416355130698</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="AG46">
+            <v>36.829284813246559</v>
+          </cell>
+          <cell r="AH46">
+            <v>4.1647733163269646E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21">
+        <row r="5">
+          <cell r="C5">
+            <v>130.89983518703079</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AG45">
+            <v>34.934198842188046</v>
+          </cell>
+          <cell r="AH45">
+            <v>4.3575177867047175E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="22">
+        <row r="29">
+          <cell r="C29">
+            <v>35.421319139716672</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="AG59">
+            <v>48.310093052891858</v>
+          </cell>
+          <cell r="AH59">
+            <v>2.6573392590665515E-4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -844,7 +1079,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -887,7 +1122,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1007,200 +1242,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="IW+_end"/>
-      <sheetName val="LCI_AD-f"/>
-      <sheetName val="LCIA_AD-f"/>
-      <sheetName val="LCIA_AD-d"/>
-      <sheetName val="LCIA_AD-c"/>
-      <sheetName val="LCI_AD-e"/>
-      <sheetName val="Waste_characteristics"/>
-      <sheetName val="Parameters"/>
-      <sheetName val="LCI"/>
-      <sheetName val="LCI_AD-d"/>
-      <sheetName val="params_HC"/>
-      <sheetName val="LCI_AD-a"/>
-      <sheetName val="LCI_AD-c"/>
-      <sheetName val="LCI_HC"/>
-      <sheetName val="LCI_AD-b"/>
-      <sheetName val="LCIA_AD-b"/>
-      <sheetName val="LCIA_HC"/>
-      <sheetName val="LCIA_AD-e"/>
-      <sheetName val="Figures"/>
-      <sheetName val="Figures_transport"/>
-      <sheetName val="IW+f"/>
-      <sheetName val="LCIA_AD-a"/>
-      <sheetName val="LCIA_IC"/>
-      <sheetName val="LCI_IC"/>
-      <sheetName val="AD_a_end"/>
-      <sheetName val="impact_process_end"/>
-      <sheetName val="impact_process_mid"/>
-      <sheetName val="IW+_mid"/>
-      <sheetName val="IC_end"/>
-      <sheetName val="AD_a_mid"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="5">
-          <cell r="C5">
-            <v>84.546284038232599</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="C51">
-            <v>-215.85245782181113</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="AG56">
-            <v>46.038360226339158</v>
-          </cell>
-          <cell r="AH56">
-            <v>4.8370041166785849E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="5">
-          <cell r="C5">
-            <v>150.20130726777239</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="AG54">
-            <v>86.06842941813477</v>
-          </cell>
-          <cell r="AH54">
-            <v>6.9920169042280941E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="5">
-          <cell r="C5">
-            <v>166.06528020235362</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="AG45">
-            <v>76.859354005042192</v>
-          </cell>
-          <cell r="AH45">
-            <v>6.3197861038764738E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15">
-        <row r="5">
-          <cell r="C5">
-            <v>115.03586225244955</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="AG55">
-            <v>44.143274255280637</v>
-          </cell>
-          <cell r="AH55">
-            <v>5.0297485870563373E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="16">
-        <row r="30">
-          <cell r="AG30">
-            <v>45.531422488575686</v>
-          </cell>
-          <cell r="AH30">
-            <v>1.5340506341983027E-4</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="C70">
-            <v>34.264521044421535</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="17">
-        <row r="5">
-          <cell r="C5">
-            <v>100.41025697281384</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="C42">
-            <v>-215.01416355130698</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="AG46">
-            <v>36.829284813246559</v>
-          </cell>
-          <cell r="AH46">
-            <v>4.1647733163269646E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21">
-        <row r="5">
-          <cell r="C5">
-            <v>130.89983518703079</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="AG45">
-            <v>34.934198842188046</v>
-          </cell>
-          <cell r="AH45">
-            <v>4.3575177867047175E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="22">
-        <row r="29">
-          <cell r="C29">
-            <v>35.421319139716672</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="AG59">
-            <v>48.310093052891858</v>
-          </cell>
-          <cell r="AH59">
-            <v>2.6573392590665515E-4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1655,15 +1697,15 @@
         <v>2.5785610221138381E-5</v>
       </c>
       <c r="I6">
-        <f>[9]LCIA_HC!$C$70</f>
+        <f>[6]LCIA_HC!$C$70</f>
         <v>34.264521044421535</v>
       </c>
       <c r="J6">
-        <f>[9]LCIA_HC!$AG$30</f>
+        <f>[6]LCIA_HC!$AG$30</f>
         <v>45.531422488575686</v>
       </c>
       <c r="K6">
-        <f>[9]LCIA_HC!$AH$30</f>
+        <f>[6]LCIA_HC!$AH$30</f>
         <v>1.5340506341983027E-4</v>
       </c>
     </row>
@@ -1675,35 +1717,35 @@
         <v>11</v>
       </c>
       <c r="C7" s="3">
-        <f>[6]LCIA_IC!$C$55 + (C3*20*[7]cop!$C$3)</f>
+        <f>[7]LCIA_IC!$C$55 + (C3*20*[8]cop!$C$3)</f>
         <v>46.680120714764449</v>
       </c>
       <c r="D7" s="3">
-        <f>[8]Feuil1!$D$7+ (D3*20*[7]cop!$C$3)</f>
+        <f>[9]Feuil1!$D$7+ (D3*20*[8]cop!$C$3)</f>
         <v>71.019913713598243</v>
       </c>
       <c r="E7" s="3">
-        <f>[8]Feuil1!$E$7+ (E3*20*[7]cop!$C$3)</f>
+        <f>[9]Feuil1!$E$7+ (E3*20*[8]cop!$C$3)</f>
         <v>2.8863191352331019E-4</v>
       </c>
       <c r="F7">
-        <f>[8]Feuil1!$F$7+ (F3*20*[7]cop!$C$3)</f>
+        <f>[9]Feuil1!$F$7+ (F3*20*[8]cop!$C$3)</f>
         <v>57.164828349042622</v>
       </c>
       <c r="G7" s="3">
-        <f>[8]Feuil1!$G$7+ (G3*20*[7]cop!$C$3)</f>
+        <f>[9]Feuil1!$G$7+ (G3*20*[8]cop!$C$3)</f>
         <v>1.0190730557336468E-4</v>
       </c>
       <c r="I7" s="4">
-        <f>[9]LCIA_IC!$C$29</f>
+        <f>[6]LCIA_IC!$C$29</f>
         <v>35.421319139716672</v>
       </c>
       <c r="J7">
-        <f>[9]LCIA_IC!$AG$59</f>
+        <f>[6]LCIA_IC!$AG$59</f>
         <v>48.310093052891858</v>
       </c>
       <c r="K7">
-        <f>[9]LCIA_IC!$AH$59</f>
+        <f>[6]LCIA_IC!$AH$59</f>
         <v>2.6573392590665515E-4</v>
       </c>
     </row>
@@ -1715,35 +1757,35 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <f>[8]Feuil1!$C$8+ (C3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$C$8+ (C3*20*[8]cop!$D$5)</f>
         <v>-80.212483537713794</v>
       </c>
       <c r="D8">
-        <f>[8]Feuil1!$D$8+ (D3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$D$8+ (D3*20*[8]cop!$D$5)</f>
         <v>-110.07998602224249</v>
       </c>
       <c r="E8" s="3">
-        <f>[8]Feuil1!$E$8+ (E3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$E$8+ (E3*20*[8]cop!$D$5)</f>
         <v>-9.8369166325107046E-4</v>
       </c>
       <c r="F8">
-        <f>[8]Feuil1!$F$8+ (F3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$F$8+ (F3*20*[8]cop!$D$5)</f>
         <v>1.0077434474601312</v>
       </c>
       <c r="G8">
-        <f>[8]Feuil1!$G$8 + (G3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$G$8 + (G3*20*[8]cop!$D$5)</f>
         <v>5.1343449163881766E-4</v>
       </c>
       <c r="I8" s="4">
-        <f>'[9]LCIA_AD-a'!$C$5</f>
+        <f>'[6]LCIA_AD-a'!$C$5</f>
         <v>130.89983518703079</v>
       </c>
       <c r="J8">
-        <f>'[9]LCIA_AD-a'!$AG$45</f>
+        <f>'[6]LCIA_AD-a'!$AG$45</f>
         <v>34.934198842188046</v>
       </c>
       <c r="K8">
-        <f>'[9]LCIA_AD-a'!$AH$45</f>
+        <f>'[6]LCIA_AD-a'!$AH$45</f>
         <v>4.3575177867047175E-4</v>
       </c>
     </row>
@@ -1755,35 +1797,35 @@
         <v>11</v>
       </c>
       <c r="C9" s="3">
-        <f>[8]Feuil1!$C$9 + (C3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$C$9 + (C3*20*[8]cop!$E$4)</f>
         <v>-82.563039563054232</v>
       </c>
       <c r="D9">
-        <f>[8]Feuil1!$D$9+ (D3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$D$9+ (D3*20*[8]cop!$E$4)</f>
         <v>-179.15476675522308</v>
       </c>
       <c r="E9" s="3">
-        <f>[8]Feuil1!$E$9 +  (E3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$E$9 +  (E3*20*[8]cop!$E$4)</f>
         <v>-1.4532776727304555E-3</v>
       </c>
       <c r="F9">
-        <f>[8]Feuil1!$F$9 + (F3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$F$9 + (F3*20*[8]cop!$E$4)</f>
         <v>-79.438110514396868</v>
       </c>
       <c r="G9">
-        <f>[8]Feuil1!$G$9 + (G3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$G$9 + (G3*20*[8]cop!$E$4)</f>
         <v>-1.0939912093601809E-4</v>
       </c>
       <c r="I9" s="4">
-        <f>'[9]LCIA_AD-b'!$C$5</f>
+        <f>'[6]LCIA_AD-b'!$C$5</f>
         <v>115.03586225244955</v>
       </c>
       <c r="J9">
-        <f>'[9]LCIA_AD-b'!$AG$55</f>
+        <f>'[6]LCIA_AD-b'!$AG$55</f>
         <v>44.143274255280637</v>
       </c>
       <c r="K9">
-        <f>'[9]LCIA_AD-b'!$AH$55</f>
+        <f>'[6]LCIA_AD-b'!$AH$55</f>
         <v>5.0297485870563373E-4</v>
       </c>
     </row>
@@ -1795,35 +1837,35 @@
         <v>11</v>
       </c>
       <c r="C10" s="3">
-        <f>[8]Feuil1!$C$10 + (C3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$C$10 + (C3*20*[8]cop!$D$5)</f>
         <v>-230.98184542684928</v>
       </c>
       <c r="D10">
-        <f>[8]Feuil1!$D$10 + (D3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$D$10 + (D3*20*[8]cop!$D$5)</f>
         <v>-111.04662553608286</v>
       </c>
       <c r="E10" s="3">
-        <f>[8]Feuil1!$E$10 + (E3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$E$10 + (E3*20*[8]cop!$D$5)</f>
         <v>-1.5179278472033484E-3</v>
       </c>
       <c r="F10">
-        <f>[8]Feuil1!$F$10 + (F3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$F$10 + (F3*20*[8]cop!$D$5)</f>
         <v>52.317652361710714</v>
       </c>
       <c r="G10">
-        <f>[8]Feuil1!$G$10 + (G3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$G$10 + (G3*20*[8]cop!$D$5)</f>
         <v>6.8372788721272372E-4</v>
       </c>
       <c r="I10" s="4">
-        <f>'[9]LCIA_AD-c'!$C$5</f>
+        <f>'[6]LCIA_AD-c'!$C$5</f>
         <v>166.06528020235362</v>
       </c>
       <c r="J10">
-        <f>'[9]LCIA_AD-c'!$AG$45</f>
+        <f>'[6]LCIA_AD-c'!$AG$45</f>
         <v>76.859354005042192</v>
       </c>
       <c r="K10">
-        <f>'[9]LCIA_AD-c'!$AH$45</f>
+        <f>'[6]LCIA_AD-c'!$AH$45</f>
         <v>6.3197861038764738E-4</v>
       </c>
     </row>
@@ -1835,35 +1877,35 @@
         <v>11</v>
       </c>
       <c r="C11" s="3">
-        <f>[8]Feuil1!$C$11 + (C3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$C$11 + (C3*20*[8]cop!$E$4)</f>
         <v>-233.33240145218971</v>
       </c>
       <c r="D11">
-        <f>[8]Feuil1!$D$11 + (D3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$D$11 + (D3*20*[8]cop!$E$4)</f>
         <v>-180.12140626906347</v>
       </c>
       <c r="E11" s="3">
-        <f>[8]Feuil1!$E$11  + (E3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$E$11  + (E3*20*[8]cop!$E$4)</f>
         <v>-1.9875138566827332E-3</v>
       </c>
       <c r="F11">
-        <f>[8]Feuil1!$F$11  + (F3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$F$11  + (F3*20*[8]cop!$E$4)</f>
         <v>-28.128201600146266</v>
       </c>
       <c r="G11">
-        <f>[8]Feuil1!$G$11  +  (G3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$G$11  +  (G3*20*[8]cop!$E$4)</f>
         <v>6.0894274637887942E-5</v>
       </c>
       <c r="I11" s="4">
-        <f>'[9]LCIA_AD-d'!$C$5</f>
+        <f>'[6]LCIA_AD-d'!$C$5</f>
         <v>150.20130726777239</v>
       </c>
       <c r="J11">
-        <f>'[9]LCIA_AD-d'!$AG$54</f>
+        <f>'[6]LCIA_AD-d'!$AG$54</f>
         <v>86.06842941813477</v>
       </c>
       <c r="K11">
-        <f>'[9]LCIA_AD-d'!$AH$54</f>
+        <f>'[6]LCIA_AD-d'!$AH$54</f>
         <v>6.9920169042280941E-4</v>
       </c>
     </row>
@@ -1875,35 +1917,35 @@
         <v>11</v>
       </c>
       <c r="C12" s="3">
-        <f>'[9]LCIA_AD-e'!$C$42 + (C3*20*[7]cop!$D$5)</f>
+        <f>'[6]LCIA_AD-e'!$C$42 + (C3*20*[8]cop!$D$5)</f>
         <v>-212.91807092217445</v>
       </c>
       <c r="D12">
-        <f>[8]Feuil1!$D$12+ (D3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$D$12+ (D3*20*[8]cop!$D$5)</f>
         <v>-176.58631777753203</v>
       </c>
       <c r="E12" s="3">
-        <f>[8]Feuil1!$E$12 + (E3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$E$12 + (E3*20*[8]cop!$D$5)</f>
         <v>-1.9347350869094899E-3</v>
       </c>
       <c r="F12">
-        <f>[8]Feuil1!$F$12 + (F3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$F$12 + (F3*20*[8]cop!$D$5)</f>
         <v>11.296443443005872</v>
       </c>
       <c r="G12">
-        <f>[8]Feuil1!$G$12 + (G3*20*[7]cop!$D$5)</f>
+        <f>[9]Feuil1!$G$12 + (G3*20*[8]cop!$D$5)</f>
         <v>5.9735562373721199E-4</v>
       </c>
       <c r="I12" s="4">
-        <f>'[9]LCIA_AD-e'!$C$5</f>
+        <f>'[6]LCIA_AD-e'!$C$5</f>
         <v>100.41025697281384</v>
       </c>
       <c r="J12">
-        <f>'[9]LCIA_AD-e'!$AG$46</f>
+        <f>'[6]LCIA_AD-e'!$AG$46</f>
         <v>36.829284813246559</v>
       </c>
       <c r="K12">
-        <f>'[9]LCIA_AD-e'!$AH$46</f>
+        <f>'[6]LCIA_AD-e'!$AH$46</f>
         <v>4.1647733163269646E-4</v>
       </c>
     </row>
@@ -1915,35 +1957,35 @@
         <v>11</v>
       </c>
       <c r="C13" s="3">
-        <f>'[9]LCIA_AD-f'!$C$51+  (C3*20*[7]cop!$E$4)</f>
+        <f>'[6]LCIA_AD-f'!$C$51+  (C3*20*[8]cop!$E$4)</f>
         <v>-215.26862694751492</v>
       </c>
       <c r="D13">
-        <f>[8]Feuil1!$D$13 + (D3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$D$13 + (D3*20*[8]cop!$E$4)</f>
         <v>-245.6610985105126</v>
       </c>
       <c r="E13" s="3">
-        <f>[8]Feuil1!$E$13 + (E3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$E$13 + (E3*20*[8]cop!$E$4)</f>
         <v>-2.4043210963888748E-3</v>
       </c>
       <c r="F13">
-        <f>[8]Feuil1!$F$13 +  (F3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$F$13 +  (F3*20*[8]cop!$E$4)</f>
         <v>-69.149410518851141</v>
       </c>
       <c r="G13">
-        <f>[8]Feuil1!$G$13 + (G3*20*[7]cop!$E$4)</f>
+        <f>[9]Feuil1!$G$13 + (G3*20*[8]cop!$E$4)</f>
         <v>-2.5477988837623735E-5</v>
       </c>
       <c r="I13" s="4">
-        <f>'[9]LCIA_AD-f'!$C$5</f>
+        <f>'[6]LCIA_AD-f'!$C$5</f>
         <v>84.546284038232599</v>
       </c>
       <c r="J13">
-        <f>'[9]LCIA_AD-f'!$AG$56</f>
+        <f>'[6]LCIA_AD-f'!$AG$56</f>
         <v>46.038360226339158</v>
       </c>
       <c r="K13">
-        <f>'[9]LCIA_AD-f'!$AH$56</f>
+        <f>'[6]LCIA_AD-f'!$AH$56</f>
         <v>4.8370041166785849E-4</v>
       </c>
     </row>
@@ -2007,8 +2049,12 @@
         <f t="shared" si="0"/>
         <v>1.9021702798128903E-7</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="M16">
+        <f>D26+(0.7318*0.702543)</f>
+        <v>0.52710343739999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2030,8 +2076,15 @@
       <c r="G17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="L17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17">
+        <f>D6-(M16*438.31)</f>
+        <v>-184.51235511861827</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2058,8 +2111,15 @@
         <f>G16</f>
         <v>1.9021702798128903E-7</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="L18" t="s">
+        <v>9</v>
+      </c>
+      <c r="M18">
+        <f>D9-M16*42.11</f>
+        <v>-201.35109250413709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2082,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2105,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -2128,12 +2188,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -2151,7 +2211,7 @@
         <v>1.3917000000000001E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2169,7 +2229,7 @@
         <v>5.1734999999999997E-6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2187,7 +2247,7 @@
         <v>5.6199000000000002E-6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -2213,7 +2273,7 @@
         <v>4.4209285281899682E-8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2231,7 +2291,7 @@
         <v>6.7176999999999999E-7</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -2249,7 +2309,7 @@
         <v>4.3286000000000003E-7</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2267,12 +2327,12 @@
         <v>3.9848000000000004E-6</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -2290,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>19</v>
       </c>

--- a/simulations/correction_peat_market/impact_brut_2 - Copie.xlsx
+++ b/simulations/correction_peat_market/impact_brut_2 - Copie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DD53F8-5FB7-46F4-A87E-95506238E84F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF23F69-BD8E-46B0-A859-B308C2829A81}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -305,7 +305,13 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0">
+        <row r="102">
+          <cell r="AG102">
+            <v>-268.34014085734225</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="AG4">
@@ -324,7 +330,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="2">
+        <row r="42">
+          <cell r="E42">
+            <v>3876.4660709036466</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
@@ -335,11 +347,41 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
+      <sheetData sheetId="13">
+        <row r="99">
+          <cell r="AG99">
+            <v>-201.83380910205278</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="14">
+        <row r="46">
+          <cell r="AG46">
+            <v>-209.55449775755659</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="15">
+        <row r="80">
+          <cell r="AG80">
+            <v>-195.86519901883881</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="16">
+        <row r="98">
+          <cell r="AG98">
+            <v>-202.80044861589312</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="17">
+        <row r="83">
+          <cell r="AG83">
+            <v>-261.40489126028797</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20">
@@ -349,8 +391,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
+      <sheetData sheetId="21">
+        <row r="81">
+          <cell r="AG81">
+            <v>-194.89855950499845</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="22">
+        <row r="84">
+          <cell r="AG84">
+            <v>-140.00263317406106</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
       <sheetData sheetId="25"/>
@@ -397,7 +451,7 @@
       <sheetName val="AD_a_mid"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="28">
           <cell r="C28">
@@ -435,19 +489,43 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
+        <row r="24">
+          <cell r="E24">
+            <v>509.03089819946877</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="24">
+          <cell r="E24">
+            <v>509.03089819946877</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="23">
+          <cell r="E23">
+            <v>131.83340888752835</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14">
+        <row r="15">
+          <cell r="E15">
+            <v>11.6046876865655</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="15">
         <row r="75">
           <cell r="C75">
@@ -455,10 +533,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19">
+        <row r="25">
+          <cell r="E25">
+            <v>9.1614439984537466</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="20">
         <row r="43">
           <cell r="C43">
@@ -466,13 +550,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
